--- a/docs/MarketingFormat_hshimizu.xlsx
+++ b/docs/MarketingFormat_hshimizu.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="企画提案書" sheetId="1" state="visible" r:id="rId3"/>
@@ -1614,7 +1614,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">例：成長市場なら将来性をアピール
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -1662,7 +1662,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">例：通勤中なら モバイルファースト設計
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -1858,100 +1858,8 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">例：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">代なら</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SNS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">連携機能
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-メインターゲットは「健康不安はあるが、日々の管理が煩雑な飼い主」に設定する。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">代にも使いやすい文字サイズ・操作性を確保しつつ、共働き層向けに家族共有
+    <t xml:space="preserve">メインターゲットは「健康不安はあるが、日々の管理が煩雑な飼い主」に設定する。50〜60代にも使いやすい文字サイズ・操作性を確保しつつ、共働き層向けに家族共有
 ・通知機能を強化する</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2027,8 +1935,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">例：情報が探しにくい→検索機能強化
-「
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -2038,7 +1945,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">不安の可視化」と「受診判断支援」を価値の中心に置く。症状チェック、異常時アラ
+      <t xml:space="preserve">「不安の可視化」と「受診判断支援」を価値の中心に置く。症状チェック、異常時アラ
 ート、履歴自動整理、予防予定の通知、医療費の見える化を主要機能に落とし込む。</t>
     </r>
   </si>
@@ -2058,25 +1965,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">例：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">SNS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">で情報収集→より信頼性の高い情報源に
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -2086,8 +1975,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">
-既存代替手段の弱点である「記録の分散」「共有しづらさ」「受診前準備の手間」を
+      <t xml:space="preserve">既存代替手段の弱点である「記録の分散」「共有しづらさ」「受診前準備の手間」を
 解消する。写真・メモ・通院履歴・ワクチン予定を一元管理し、家族や獣医師に見せや
 すい形で出力できる設計にする。</t>
     </r>
@@ -2109,7 +1997,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">例：利便性重視→ワンクリック操作
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -2169,44 +2057,20 @@
     <t xml:space="preserve">主要競合サービス（3〜5個）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CoDMON</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">（コドモン）、ルクミー、はいチーズ！システム、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">hugnote</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">（ハグノート）
-いずれも保育施設向けに、登降園管理・連絡帳・帳票作成・請求・安全管理・保護者
-連携を広くカバーする主要プレイヤー。</t>
-    </r>
+    <t xml:space="preserve">animo、みるペット、アニぴたる、MinePet。
+animoは症状・服薬記録と獣医共有に強い健康管理アプリ。みるペットはオンライン相談・診療・予約・決済に強い。アニぴたるは獣医師へのオンライン相談と検索に強い。MinePetは日常記録と通院記録の一元管理に強い。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">競合定義を「単機能アプリ」ではなく、①健康記録系、②オンライン相談・診療系、③獣医接続系の3類型で整理する。自作品はそれらを横断する統合型として位置づける。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">animoは症状記録、服薬管理、カレンダー管理、獣医共有、対応病院でのオンライン診療導線を持つ。みるペットはビデオ通話、24時間WEB予約、オンライン決済、再診リマインドまで整っている。アニぴたるは初回無料相談、獣医師の得意分野検索、複数回答の可能性が強み。MinePetは写真・動画・テキストによる日常記録と通院記録の蓄積に強い。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自作品でも「記録のしやすさ」「相談のしやすさ」「次行動の分かりやすさ」を中核価値として明示する。特に、記録が受診判断や相談準備に直結する設計を強みにする。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">animoは記録と共有に強い一方、サービス全体としては特定病院連携前提があり、生活者向け総合プラットフォーム性は限定的。みるペットは診療導線が強い一方で、日常健康データの継続蓄積は主軸ではない。アニぴたるは相談特化で、リアルタイム診療や処方、日常記録の統合は弱い。MinePetは記録中心で、相談・診療・予約機能の統合はまだ弱い。</t>
   </si>
   <si>
     <r>
@@ -2216,334 +2080,30 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">例：競合A、B、Cを分析対象に
+      <t xml:space="preserve">自作品では、単発相談や単なる記録で終わらず、「日常記録→異変検知→相談→診療予約→履歴管理」まで切れ目なくつなぐ設計を前面に出す。
 </t>
     </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">
-競合定義を「保育</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">の総合型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SaaS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">」に絞る。以後の企画・訴求は、単機能比較では
-なく総合業務体験の比較で設計する。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CoDMON</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">は導入施設数・自治体導入・継続率・機能幅で強い。標準機能の網羅性が高
-く、価格の入口も低めで、自治体や複数施設運営まで対応できる総合力がある。
-「大手で安心」「長く使える標準システム」という印象が強い。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">例：ブランド力→差別化要素を明確に
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">
-自社作品でも、情緒的価値だけでなく、業務削減・連絡効率化・安全管理の3軸を
-必須要素として明示する。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Serif"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CoDMON</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">：総合力は高いが、機能範囲が広いため、新規導入時は設定・運用設計の
-検討項目が増えやすい。標準機能が強い反面、個別園の細かい運用差には調整負荷が
-出る余地がある。
-総論として、総合型競合は「多機能ゆえの複雑さ」、コミュニケーション型競合は
-「深い業務最適化の限界」が弱みになりやすい</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">例：使いづらいUI→シンプルなUIで差別化
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">
-自社作品では「多機能」よりも、初期設定の簡単さ、定着のしやすさ、特定課題の
-解決速度を前面に出す。特に、導入直後から成果が見える一点突破型の訴求にすると
-競合との差が出しやすい。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">はいチーズ！システムは初期費用・月額利用料</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">円訴求と</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">以上の機能で導入ハードル
-を下げやすい。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">hugnote</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">は連絡帳・お知らせ・写真共有・申請に加え、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">QR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">打刻・請求・
-日誌までつながっており、保護者アプリ体験が強い。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">例：月額制が主流→無料プランで訴求
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">
-自社作品では、価格だけでなく「導入しやすさ」「現場定着しやすさ」「保護者が
-迷わないUI」の3点を差別化軸として盛り込む</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CoDMON</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">：業務支援ツールらしい情報整理型。トップ訴求も「入退室・連絡・帳票・
-請求」など機能軸が明確で、安心感・標準性・実務性を重視した設計。
-総論として、競合は「業務効率型」「体験価値型」「導入しやすさ型」に大別できる。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">例：モダン・シンプル・カラフル等
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">
-自社作品の見せ方を決める際は、①信頼感重視なら CoDMON 型、②共感・体験重視
-なら ルクミー型、③導入障壁の低さ重視なら はいチーズ！型、④保護者接点重視なら
- Hugnote 型を参考にする。差別化するなら、温かさと業務効率の両立が有効。</t>
-    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">animoはApp Store上で無料、アプリ内課金あり。みるペットは飼い主登録費用・月額固定費用は無料で、オンライン相談・診療1回ごとに300円税抜、チャット相談1件ごとに100円税抜、別途病院側の診療費等が発生。アニぴたるはお試しプラン0円、月額330円税込のスタンダード、年額3,300円税込の年間プランがある。MinePetはβ版提供中で、公開ページ上では一般向け料金の明確な提示は限定的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自作品は無料で始められる導入設計を基本にしつつ、AI症状チェック、オンライン診療連携、訪問ケア予約などを段階課金にする。価格訴求よりも、安心感と継続利用価値を重視する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">animoは医療・記録系らしい実務寄りUIで、症状や服薬を整理して共有する設計が中心。みるペットは予約・受診導線が分かりやすく、通院負担軽減をストレートに訴求する実用型。アニぴたるは親しみやすさと信頼感を両立し、相談投稿や獣医検索に入りやすい構成。MinePetはやさしいトーンで、健康記録を日常に溶け込ませるシンプル設計。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自作品は、医療サービスとしての信頼感を保ちつつ、忙しい飼い主でも続けやすい温かいUIにする。トップでは「安心」「簡単」「すぐ相談できる」を同時に伝える。</t>
   </si>
   <si>
     <t xml:space="preserve">差別化ポイント（自作品との違い）</t>
   </si>
   <si>
-    <t xml:space="preserve">総合型競合は強い一方、広く浅くなりやすい。勝ち筋は、①特定施設類型特化、
-②特定業務の圧倒的深掘り、③導入・定着支援の手厚さ、④既存帳票や運用への適応力、
-⑤AIによる記録・監査・要約支援など。特に「多機能」より「現場の手間が確実に減る
-一点突破」の方が新規参入では刺さりやすい。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">例：○○機能、△△な体験
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">作品全体のコンセプトを「全部できる」ではなく、「この現場課題だけは最短で解決
-できる」に寄せる。訴求対象も全園ではなく、施設類型や運営課題で絞る。</t>
-    </r>
+    <t xml:space="preserve">既存競合は、記録、相談、診療、検索のいずれかに強みが偏る傾向がある。一方、自作品は、健康データの一元管理、AI症状チェック、オンライン相談・診療、訪問ケア連携を一つの体験に統合できる点が差別化要素になる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作品全体の訴求は「全部入り」ではなく、「忙しい飼い主が、迷わず次行動を取れる健康管理基盤」として表現する。特に、家族共有、受診判断、診療後の継続管理までつながる点をコア価値にする。</t>
   </si>
   <si>
     <r>
@@ -2663,7 +2223,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">例：React使える→動的UI実装可能
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -2685,27 +2245,10 @@
     <t xml:space="preserve">飼い主が抱える「日常の健康管理が続かない」「異変時に受診判断しづらい」「情報が分散して家族共有しにくい」という課題に対し、予防から受診前後までを一元化した体験を提案することが目的。ペットの家族化・健康意識の上昇という市場背景に対し、記録アプリではなく“健康管理プラットフォーム”として価値を示す。</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">例：フロントエンド技術をアピー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">ル
+    <t xml:space="preserve">
 企画書・画面構成・訴求文はすべて「安心」「継続しやすさ」「受診につながる実用
 性」を軸に統一する。トップページでは課題解決型の導入にし、機能説明より先に
 利用価値を伝える構成にする。</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2744,7 +2287,8 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">例：前職の業界知識→リアルな課題設</t>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -2753,7 +2297,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">定
+      <t xml:space="preserve">
 作品では、①ホームで今日やることが分かる、②異変時に迷わず次行動へ進める、
 ③家族や獣医師に共有しやすい、の3点をコア体験として表現する。機能数の多さで
 はなく、利用文脈のつながりを強みとして見せる。</t>
@@ -2817,7 +2361,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">例：3週間→MVP的にスコープを絞る
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -2872,7 +2416,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">例：実務レベルのUI/UX設計力を評価
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -5075,7 +4619,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="54">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5277,6 +4821,20 @@
     </font>
     <font>
       <sz val="8"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Noto Sans"/>
       <family val="2"/>
       <charset val="1"/>
@@ -5288,15 +4846,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Noto Sans"/>
+      <sz val="8"/>
+      <name val="Tahoma"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Noto Serif"/>
-      <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
@@ -5851,7 +5403,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="214">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6056,6 +5608,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6064,6 +5620,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="32" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6076,7 +5636,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6084,11 +5644,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="35" fillId="6" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="13" fillId="6" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6096,51 +5664,55 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="35" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="6" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="6" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="6" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="9" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="36" fillId="9" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="9" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="37" fillId="9" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6168,7 +5740,7 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6180,7 +5752,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6188,11 +5760,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="6" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="42" fillId="6" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6200,11 +5772,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="38" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6212,7 +5784,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6224,51 +5796,51 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="9" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="10" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="38" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="9" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="10" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="11" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="37" fillId="11" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6276,11 +5848,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="11" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="37" fillId="11" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6288,11 +5860,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="11" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="37" fillId="11" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6304,7 +5876,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6320,7 +5892,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6360,7 +5932,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6388,7 +5960,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="45" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6396,15 +5972,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="46" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="47" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6412,18 +5984,18 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="48" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6432,7 +6004,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6460,7 +6032,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="41" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="41" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6472,7 +6044,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6484,7 +6056,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6588,7 +6160,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="49" fillId="14" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="50" fillId="14" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6600,7 +6172,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6608,7 +6180,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6620,7 +6192,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6628,7 +6200,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="51" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8447,16 +8019,16 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="42.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="51" width="42.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>253</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
@@ -8467,226 +8039,226 @@
       <c r="D2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="54" t="s">
         <v>255</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" s="54" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="55" t="s">
         <v>257</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="56" t="s">
         <v>258</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="57" t="s">
         <v>259</v>
       </c>
-      <c r="D5" s="56" t="s">
+      <c r="D5" s="58" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="53"/>
-      <c r="B6" s="57" t="s">
+      <c r="A6" s="55"/>
+      <c r="B6" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="61" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="53"/>
-      <c r="B7" s="57" t="s">
+      <c r="A7" s="55"/>
+      <c r="B7" s="59" t="s">
         <v>263</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="62" t="s">
         <v>264</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="63" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="53"/>
-      <c r="B8" s="57" t="s">
+      <c r="A8" s="55"/>
+      <c r="B8" s="59" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="62" t="s">
         <v>266</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="61" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="53"/>
-      <c r="B9" s="57" t="s">
+      <c r="A9" s="55"/>
+      <c r="B9" s="59" t="s">
         <v>268</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="D9" s="59" t="s">
+      <c r="D9" s="61" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="53"/>
-      <c r="B10" s="60" t="s">
+      <c r="A10" s="55"/>
+      <c r="B10" s="64" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="61" t="s">
+      <c r="C10" s="65" t="s">
         <v>272</v>
       </c>
-      <c r="D10" s="62" t="s">
+      <c r="D10" s="66" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="63" t="s">
+      <c r="A11" s="67" t="s">
         <v>274</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="56" t="s">
         <v>275</v>
       </c>
-      <c r="C11" s="64" t="s">
+      <c r="C11" s="57" t="s">
         <v>276</v>
       </c>
-      <c r="D11" s="65" t="s">
+      <c r="D11" s="68" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="63"/>
-      <c r="B12" s="57" t="s">
+      <c r="A12" s="67"/>
+      <c r="B12" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="60" t="s">
         <v>278</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="63" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="63"/>
-      <c r="B13" s="57" t="s">
+      <c r="A13" s="67"/>
+      <c r="B13" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="60" t="s">
         <v>280</v>
       </c>
-      <c r="D13" s="67" t="s">
+      <c r="D13" s="69" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="63"/>
-      <c r="B14" s="57" t="s">
+      <c r="A14" s="67"/>
+      <c r="B14" s="59" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="60" t="s">
         <v>282</v>
       </c>
-      <c r="D14" s="67" t="s">
+      <c r="D14" s="63" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="63"/>
-      <c r="B15" s="57" t="s">
+      <c r="A15" s="67"/>
+      <c r="B15" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="60" t="s">
         <v>284</v>
       </c>
-      <c r="D15" s="67" t="s">
+      <c r="D15" s="63" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="63"/>
-      <c r="B16" s="60" t="s">
+      <c r="A16" s="67"/>
+      <c r="B16" s="64" t="s">
         <v>286</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="65" t="s">
         <v>287</v>
       </c>
-      <c r="D16" s="69" t="s">
+      <c r="D16" s="70" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="70" t="s">
+      <c r="A17" s="71" t="s">
         <v>289</v>
       </c>
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="56" t="s">
         <v>290</v>
       </c>
-      <c r="C17" s="55" t="s">
+      <c r="C17" s="57" t="s">
         <v>291</v>
       </c>
-      <c r="D17" s="65" t="s">
+      <c r="D17" s="72" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="70"/>
-      <c r="B18" s="57" t="s">
+      <c r="A18" s="71"/>
+      <c r="B18" s="59" t="s">
         <v>293</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="60" t="s">
         <v>294</v>
       </c>
-      <c r="D18" s="67" t="s">
+      <c r="D18" s="73" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="70"/>
-      <c r="B19" s="57" t="s">
+      <c r="A19" s="71"/>
+      <c r="B19" s="59" t="s">
         <v>147</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="62" t="s">
         <v>296</v>
       </c>
-      <c r="D19" s="67" t="s">
+      <c r="D19" s="69" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="70"/>
-      <c r="B20" s="57" t="s">
+      <c r="A20" s="71"/>
+      <c r="B20" s="59" t="s">
         <v>298</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="62" t="s">
         <v>299</v>
       </c>
-      <c r="D20" s="67" t="s">
+      <c r="D20" s="69" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="70"/>
-      <c r="B21" s="60" t="s">
+      <c r="A21" s="71"/>
+      <c r="B21" s="64" t="s">
         <v>301</v>
       </c>
-      <c r="C21" s="61" t="s">
+      <c r="C21" s="74" t="s">
         <v>302</v>
       </c>
-      <c r="D21" s="69" t="s">
+      <c r="D21" s="75" t="s">
         <v>303</v>
       </c>
     </row>
@@ -8749,55 +8321,55 @@
       <c r="G2" s="33"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="76" t="s">
         <v>307</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71" t="s">
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76" t="s">
         <v>308</v>
       </c>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="77" t="s">
         <v>309</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="78" t="s">
         <v>310</v>
       </c>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="74" t="s">
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="79" t="s">
         <v>311</v>
       </c>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="J5" s="75" t="s">
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="J5" s="80" t="s">
         <v>312</v>
       </c>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="72"/>
-      <c r="B6" s="76" t="s">
+      <c r="A6" s="77"/>
+      <c r="B6" s="81" t="s">
         <v>158</v>
       </c>
-      <c r="C6" s="77" t="s">
+      <c r="C6" s="82" t="s">
         <v>313</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="83" t="s">
         <v>314</v>
       </c>
-      <c r="E6" s="76" t="s">
+      <c r="E6" s="81" t="s">
         <v>158</v>
       </c>
-      <c r="F6" s="77" t="s">
+      <c r="F6" s="82" t="s">
         <v>313</v>
       </c>
-      <c r="G6" s="78" t="s">
+      <c r="G6" s="83" t="s">
         <v>315</v>
       </c>
       <c r="J6" s="36" t="s">
@@ -8811,23 +8383,23 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="72"/>
-      <c r="B7" s="79" t="s">
+      <c r="A7" s="77"/>
+      <c r="B7" s="84" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="80" t="s">
+      <c r="C7" s="85" t="s">
         <v>317</v>
       </c>
-      <c r="D7" s="81" t="s">
+      <c r="D7" s="86" t="s">
         <v>318</v>
       </c>
-      <c r="E7" s="82" t="s">
+      <c r="E7" s="87" t="s">
         <v>319</v>
       </c>
-      <c r="F7" s="83" t="s">
+      <c r="F7" s="88" t="s">
         <v>320</v>
       </c>
-      <c r="G7" s="81" t="s">
+      <c r="G7" s="86" t="s">
         <v>321</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -8839,23 +8411,23 @@
       <c r="L7" s="41"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="72"/>
-      <c r="B8" s="84" t="s">
+      <c r="A8" s="77"/>
+      <c r="B8" s="89" t="s">
         <v>324</v>
       </c>
-      <c r="C8" s="85" t="s">
+      <c r="C8" s="90" t="s">
         <v>325</v>
       </c>
-      <c r="D8" s="86" t="s">
+      <c r="D8" s="91" t="s">
         <v>326</v>
       </c>
-      <c r="E8" s="87" t="s">
+      <c r="E8" s="92" t="s">
         <v>327</v>
       </c>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="62" t="s">
         <v>328</v>
       </c>
-      <c r="G8" s="86" t="s">
+      <c r="G8" s="91" t="s">
         <v>329</v>
       </c>
       <c r="J8" s="1" t="s">
@@ -8867,23 +8439,23 @@
       <c r="L8" s="41"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="72"/>
-      <c r="B9" s="88" t="s">
+      <c r="A9" s="77"/>
+      <c r="B9" s="93" t="s">
         <v>332</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="62" t="s">
         <v>333</v>
       </c>
-      <c r="D9" s="89" t="s">
+      <c r="D9" s="94" t="s">
         <v>334</v>
       </c>
-      <c r="E9" s="87" t="s">
+      <c r="E9" s="92" t="s">
         <v>335</v>
       </c>
-      <c r="F9" s="58" t="s">
+      <c r="F9" s="62" t="s">
         <v>336</v>
       </c>
-      <c r="G9" s="86" t="s">
+      <c r="G9" s="91" t="s">
         <v>337</v>
       </c>
       <c r="J9" s="1" t="s">
@@ -8895,23 +8467,23 @@
       <c r="L9" s="41"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="72"/>
-      <c r="B10" s="90" t="s">
+      <c r="A10" s="77"/>
+      <c r="B10" s="95" t="s">
         <v>340</v>
       </c>
-      <c r="C10" s="91" t="s">
+      <c r="C10" s="96" t="s">
         <v>341</v>
       </c>
-      <c r="D10" s="92" t="s">
+      <c r="D10" s="97" t="s">
         <v>342</v>
       </c>
-      <c r="E10" s="93" t="s">
+      <c r="E10" s="98" t="s">
         <v>343</v>
       </c>
-      <c r="F10" s="91" t="s">
+      <c r="F10" s="96" t="s">
         <v>344</v>
       </c>
-      <c r="G10" s="92" t="s">
+      <c r="G10" s="97" t="s">
         <v>345</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -8921,204 +8493,204 @@
       <c r="L10" s="41"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="94" t="s">
+      <c r="A11" s="99" t="s">
         <v>347</v>
       </c>
-      <c r="B11" s="95" t="s">
+      <c r="B11" s="100" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="95"/>
-      <c r="D11" s="95"/>
-      <c r="E11" s="96" t="s">
+      <c r="C11" s="100"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="101" t="s">
         <v>348</v>
       </c>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="94"/>
-      <c r="B12" s="76" t="s">
+      <c r="A12" s="99"/>
+      <c r="B12" s="81" t="s">
         <v>158</v>
       </c>
-      <c r="C12" s="77" t="s">
+      <c r="C12" s="82" t="s">
         <v>313</v>
       </c>
-      <c r="D12" s="78" t="s">
+      <c r="D12" s="83" t="s">
         <v>314</v>
       </c>
-      <c r="E12" s="76" t="s">
+      <c r="E12" s="81" t="s">
         <v>158</v>
       </c>
-      <c r="F12" s="77" t="s">
+      <c r="F12" s="82" t="s">
         <v>313</v>
       </c>
-      <c r="G12" s="78" t="s">
+      <c r="G12" s="83" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="94"/>
-      <c r="B13" s="97" t="s">
+      <c r="A13" s="99"/>
+      <c r="B13" s="102" t="s">
         <v>350</v>
       </c>
-      <c r="C13" s="83" t="s">
+      <c r="C13" s="88" t="s">
         <v>351</v>
       </c>
-      <c r="D13" s="81" t="s">
+      <c r="D13" s="86" t="s">
         <v>352</v>
       </c>
-      <c r="E13" s="97" t="s">
+      <c r="E13" s="102" t="s">
         <v>353</v>
       </c>
-      <c r="F13" s="98" t="s">
+      <c r="F13" s="103" t="s">
         <v>354</v>
       </c>
-      <c r="G13" s="81" t="s">
+      <c r="G13" s="86" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="94"/>
-      <c r="B14" s="88" t="s">
+      <c r="A14" s="99"/>
+      <c r="B14" s="93" t="s">
         <v>356</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="62" t="s">
         <v>357</v>
       </c>
-      <c r="D14" s="86" t="s">
+      <c r="D14" s="91" t="s">
         <v>358</v>
       </c>
-      <c r="E14" s="99" t="s">
+      <c r="E14" s="104" t="s">
         <v>359</v>
       </c>
-      <c r="F14" s="58" t="s">
+      <c r="F14" s="62" t="s">
         <v>360</v>
       </c>
-      <c r="G14" s="86" t="s">
+      <c r="G14" s="91" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="94"/>
-      <c r="B15" s="99" t="s">
+      <c r="A15" s="99"/>
+      <c r="B15" s="104" t="s">
         <v>362</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="D15" s="86" t="s">
+      <c r="D15" s="91" t="s">
         <v>364</v>
       </c>
-      <c r="E15" s="87" t="s">
+      <c r="E15" s="92" t="s">
         <v>365</v>
       </c>
-      <c r="F15" s="58" t="s">
+      <c r="F15" s="62" t="s">
         <v>366</v>
       </c>
-      <c r="G15" s="100" t="s">
+      <c r="G15" s="105" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="94"/>
-      <c r="B16" s="101" t="s">
+      <c r="A16" s="99"/>
+      <c r="B16" s="106" t="s">
         <v>368</v>
       </c>
-      <c r="C16" s="91" t="s">
+      <c r="C16" s="96" t="s">
         <v>369</v>
       </c>
-      <c r="D16" s="92" t="s">
+      <c r="D16" s="97" t="s">
         <v>370</v>
       </c>
-      <c r="E16" s="93" t="s">
+      <c r="E16" s="98" t="s">
         <v>371</v>
       </c>
-      <c r="F16" s="91" t="s">
+      <c r="F16" s="96" t="s">
         <v>372</v>
       </c>
-      <c r="G16" s="92" t="s">
+      <c r="G16" s="97" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="102" t="s">
+      <c r="B18" s="107" t="s">
         <v>374</v>
       </c>
-      <c r="C18" s="102"/>
-      <c r="D18" s="102"/>
-      <c r="E18" s="102"/>
-      <c r="F18" s="102"/>
-      <c r="G18" s="102"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="107"/>
+      <c r="G18" s="107"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="77" t="s">
+      <c r="B19" s="82" t="s">
         <v>375</v>
       </c>
-      <c r="C19" s="77" t="s">
+      <c r="C19" s="82" t="s">
         <v>376</v>
       </c>
-      <c r="D19" s="77" t="s">
+      <c r="D19" s="82" t="s">
         <v>377</v>
       </c>
-      <c r="E19" s="77"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="77"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="82"/>
     </row>
     <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="103" t="s">
+      <c r="B20" s="108" t="s">
         <v>378</v>
       </c>
-      <c r="C20" s="104" t="s">
+      <c r="C20" s="109" t="s">
         <v>379</v>
       </c>
-      <c r="D20" s="105" t="s">
+      <c r="D20" s="110" t="s">
         <v>380</v>
       </c>
-      <c r="E20" s="105"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="105"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="110"/>
+      <c r="G20" s="110"/>
     </row>
     <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="106" t="s">
+      <c r="B21" s="111" t="s">
         <v>381</v>
       </c>
-      <c r="C21" s="107" t="s">
+      <c r="C21" s="112" t="s">
         <v>382</v>
       </c>
-      <c r="D21" s="108" t="s">
+      <c r="D21" s="113" t="s">
         <v>383</v>
       </c>
-      <c r="E21" s="108"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="108"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
     </row>
     <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="106" t="s">
+      <c r="B22" s="111" t="s">
         <v>384</v>
       </c>
-      <c r="C22" s="107" t="s">
+      <c r="C22" s="112" t="s">
         <v>385</v>
       </c>
-      <c r="D22" s="108" t="s">
+      <c r="D22" s="113" t="s">
         <v>386</v>
       </c>
-      <c r="E22" s="108"/>
-      <c r="F22" s="108"/>
-      <c r="G22" s="108"/>
+      <c r="E22" s="113"/>
+      <c r="F22" s="113"/>
+      <c r="G22" s="113"/>
     </row>
     <row r="23" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="109" t="s">
+      <c r="B23" s="114" t="s">
         <v>387</v>
       </c>
-      <c r="C23" s="110" t="s">
+      <c r="C23" s="115" t="s">
         <v>388</v>
       </c>
-      <c r="D23" s="111" t="s">
+      <c r="D23" s="116" t="s">
         <v>389</v>
       </c>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="111"/>
+      <c r="E23" s="116"/>
+      <c r="F23" s="116"/>
+      <c r="G23" s="116"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="39" t="s">
@@ -9195,13 +8767,13 @@
       <c r="E2" s="33"/>
     </row>
     <row r="4" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="112" t="s">
+      <c r="A4" s="117" t="s">
         <v>393</v>
       </c>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="39" t="s">
@@ -9230,93 +8802,93 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="118" t="s">
         <v>400</v>
       </c>
-      <c r="B7" s="114" t="s">
+      <c r="B7" s="119" t="s">
         <v>401</v>
       </c>
-      <c r="C7" s="115" t="s">
+      <c r="C7" s="120" t="s">
         <v>402</v>
       </c>
-      <c r="D7" s="114" t="s">
+      <c r="D7" s="119" t="s">
         <v>403</v>
       </c>
-      <c r="E7" s="116" t="s">
+      <c r="E7" s="121" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="117" t="s">
+      <c r="A8" s="122" t="s">
         <v>405</v>
       </c>
-      <c r="B8" s="118" t="s">
+      <c r="B8" s="123" t="s">
         <v>406</v>
       </c>
-      <c r="C8" s="119" t="s">
+      <c r="C8" s="124" t="s">
         <v>407</v>
       </c>
-      <c r="D8" s="118" t="s">
+      <c r="D8" s="123" t="s">
         <v>408</v>
       </c>
-      <c r="E8" s="120" t="s">
+      <c r="E8" s="125" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="117" t="s">
+      <c r="A9" s="122" t="s">
         <v>410</v>
       </c>
-      <c r="B9" s="118" t="s">
+      <c r="B9" s="123" t="s">
         <v>411</v>
       </c>
-      <c r="C9" s="119" t="s">
+      <c r="C9" s="124" t="s">
         <v>412</v>
       </c>
-      <c r="D9" s="121" t="s">
+      <c r="D9" s="126" t="s">
         <v>413</v>
       </c>
-      <c r="E9" s="120" t="s">
+      <c r="E9" s="125" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="117" t="s">
+      <c r="A10" s="122" t="s">
         <v>415</v>
       </c>
-      <c r="B10" s="118" t="s">
+      <c r="B10" s="123" t="s">
         <v>416</v>
       </c>
-      <c r="C10" s="119" t="s">
+      <c r="C10" s="124" t="s">
         <v>412</v>
       </c>
-      <c r="D10" s="118" t="s">
+      <c r="D10" s="123" t="s">
         <v>417</v>
       </c>
-      <c r="E10" s="120" t="s">
+      <c r="E10" s="125" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="122" t="s">
+      <c r="A11" s="127" t="s">
         <v>419</v>
       </c>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="123" t="s">
+      <c r="A16" s="128" t="s">
         <v>420</v>
       </c>
-      <c r="B16" s="123"/>
-      <c r="C16" s="123"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="123"/>
+      <c r="B16" s="128"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="128"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="39" t="s">
@@ -9328,68 +8900,68 @@
       <c r="E17" s="39"/>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="124" t="s">
+      <c r="A18" s="129" t="s">
         <v>422</v>
       </c>
-      <c r="B18" s="125" t="s">
+      <c r="B18" s="130" t="s">
         <v>423</v>
       </c>
-      <c r="C18" s="126"/>
-      <c r="D18" s="126"/>
-      <c r="E18" s="126"/>
+      <c r="C18" s="131"/>
+      <c r="D18" s="131"/>
+      <c r="E18" s="131"/>
     </row>
     <row r="19" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="127" t="s">
+      <c r="A19" s="132" t="s">
         <v>424</v>
       </c>
-      <c r="B19" s="128" t="s">
+      <c r="B19" s="133" t="s">
         <v>425</v>
       </c>
-      <c r="C19" s="128"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="128"/>
+      <c r="C19" s="133"/>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="41"/>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="124" t="s">
+      <c r="A21" s="129" t="s">
         <v>426</v>
       </c>
-      <c r="B21" s="126"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="126"/>
-      <c r="E21" s="126"/>
+      <c r="B21" s="131"/>
+      <c r="C21" s="131"/>
+      <c r="D21" s="131"/>
+      <c r="E21" s="131"/>
     </row>
     <row r="22" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="129" t="s">
+      <c r="A22" s="134" t="s">
         <v>427</v>
       </c>
-      <c r="B22" s="129"/>
-      <c r="C22" s="129"/>
-      <c r="D22" s="129"/>
-      <c r="E22" s="129"/>
+      <c r="B22" s="134"/>
+      <c r="C22" s="134"/>
+      <c r="D22" s="134"/>
+      <c r="E22" s="134"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="41"/>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="124" t="s">
+      <c r="A24" s="129" t="s">
         <v>428</v>
       </c>
-      <c r="B24" s="126"/>
-      <c r="C24" s="126"/>
-      <c r="D24" s="126"/>
-      <c r="E24" s="126"/>
+      <c r="B24" s="131"/>
+      <c r="C24" s="131"/>
+      <c r="D24" s="131"/>
+      <c r="E24" s="131"/>
     </row>
     <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="130" t="s">
+      <c r="A25" s="135" t="s">
         <v>429</v>
       </c>
-      <c r="B25" s="130"/>
-      <c r="C25" s="130"/>
-      <c r="D25" s="130"/>
-      <c r="E25" s="130"/>
+      <c r="B25" s="135"/>
+      <c r="C25" s="135"/>
+      <c r="D25" s="135"/>
+      <c r="E25" s="135"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="39" t="s">
@@ -9404,13 +8976,13 @@
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="131" t="s">
+      <c r="A31" s="136" t="s">
         <v>431</v>
       </c>
-      <c r="B31" s="131"/>
-      <c r="C31" s="131"/>
-      <c r="D31" s="131"/>
-      <c r="E31" s="131"/>
+      <c r="B31" s="136"/>
+      <c r="C31" s="136"/>
+      <c r="D31" s="136"/>
+      <c r="E31" s="136"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="39" t="s">
@@ -9422,85 +8994,85 @@
       <c r="E32" s="39"/>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="124" t="s">
+      <c r="A33" s="129" t="s">
         <v>433</v>
       </c>
-      <c r="B33" s="126"/>
-      <c r="C33" s="126"/>
-      <c r="D33" s="126"/>
-      <c r="E33" s="126"/>
+      <c r="B33" s="131"/>
+      <c r="C33" s="131"/>
+      <c r="D33" s="131"/>
+      <c r="E33" s="131"/>
     </row>
     <row r="34" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="132" t="s">
+      <c r="A34" s="137" t="s">
         <v>434</v>
       </c>
-      <c r="B34" s="132"/>
-      <c r="C34" s="132"/>
-      <c r="D34" s="132"/>
-      <c r="E34" s="132"/>
+      <c r="B34" s="137"/>
+      <c r="C34" s="137"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="137"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="41"/>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="124" t="s">
+      <c r="A36" s="129" t="s">
         <v>435</v>
       </c>
-      <c r="B36" s="126"/>
-      <c r="C36" s="126"/>
-      <c r="D36" s="126"/>
-      <c r="E36" s="126"/>
+      <c r="B36" s="131"/>
+      <c r="C36" s="131"/>
+      <c r="D36" s="131"/>
+      <c r="E36" s="131"/>
     </row>
     <row r="37" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="133" t="s">
+      <c r="A37" s="138" t="s">
         <v>436</v>
       </c>
-      <c r="B37" s="133"/>
-      <c r="C37" s="133"/>
-      <c r="D37" s="133"/>
-      <c r="E37" s="133"/>
+      <c r="B37" s="138"/>
+      <c r="C37" s="138"/>
+      <c r="D37" s="138"/>
+      <c r="E37" s="138"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="41"/>
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="124" t="s">
+      <c r="A39" s="129" t="s">
         <v>437</v>
       </c>
-      <c r="B39" s="126"/>
-      <c r="C39" s="126"/>
-      <c r="D39" s="126"/>
-      <c r="E39" s="126"/>
+      <c r="B39" s="131"/>
+      <c r="C39" s="131"/>
+      <c r="D39" s="131"/>
+      <c r="E39" s="131"/>
     </row>
     <row r="40" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="133" t="s">
+      <c r="A40" s="138" t="s">
         <v>438</v>
       </c>
-      <c r="B40" s="133"/>
-      <c r="C40" s="133"/>
-      <c r="D40" s="133"/>
-      <c r="E40" s="133"/>
+      <c r="B40" s="138"/>
+      <c r="C40" s="138"/>
+      <c r="D40" s="138"/>
+      <c r="E40" s="138"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="41"/>
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="124" t="s">
+      <c r="A42" s="129" t="s">
         <v>439</v>
       </c>
-      <c r="B42" s="126"/>
-      <c r="C42" s="126"/>
-      <c r="D42" s="126"/>
-      <c r="E42" s="126"/>
+      <c r="B42" s="131"/>
+      <c r="C42" s="131"/>
+      <c r="D42" s="131"/>
+      <c r="E42" s="131"/>
     </row>
     <row r="43" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="132" t="s">
+      <c r="A43" s="137" t="s">
         <v>440</v>
       </c>
-      <c r="B43" s="132"/>
-      <c r="C43" s="132"/>
-      <c r="D43" s="132"/>
-      <c r="E43" s="132"/>
+      <c r="B43" s="137"/>
+      <c r="C43" s="137"/>
+      <c r="D43" s="137"/>
+      <c r="E43" s="137"/>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="39" t="s">
@@ -9706,122 +9278,122 @@
       <c r="F2" s="33"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="134" t="s">
+      <c r="B4" s="139" t="s">
         <v>465</v>
       </c>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="134"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="135" t="s">
+      <c r="A6" s="140" t="s">
         <v>466</v>
       </c>
-      <c r="B6" s="136" t="s">
+      <c r="B6" s="141" t="s">
         <v>467</v>
       </c>
-      <c r="C6" s="136" t="s">
+      <c r="C6" s="141" t="s">
         <v>468</v>
       </c>
-      <c r="D6" s="136" t="s">
+      <c r="D6" s="141" t="s">
         <v>469</v>
       </c>
-      <c r="E6" s="136" t="s">
+      <c r="E6" s="141" t="s">
         <v>470</v>
       </c>
-      <c r="F6" s="137" t="s">
+      <c r="F6" s="142" t="s">
         <v>471</v>
       </c>
       <c r="G6" s="45"/>
     </row>
     <row r="7" customFormat="false" ht="106.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="138" t="s">
+      <c r="A7" s="143" t="s">
         <v>472</v>
       </c>
-      <c r="B7" s="139" t="s">
+      <c r="B7" s="144" t="s">
         <v>473</v>
       </c>
-      <c r="C7" s="139" t="s">
+      <c r="C7" s="144" t="s">
         <v>474</v>
       </c>
-      <c r="D7" s="140" t="s">
+      <c r="D7" s="145" t="s">
         <v>475</v>
       </c>
-      <c r="E7" s="139" t="s">
+      <c r="E7" s="144" t="s">
         <v>476</v>
       </c>
-      <c r="F7" s="140" t="s">
+      <c r="F7" s="145" t="s">
         <v>477</v>
       </c>
-      <c r="G7" s="141"/>
-      <c r="H7" s="141"/>
+      <c r="G7" s="146"/>
+      <c r="H7" s="146"/>
     </row>
     <row r="8" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="138" t="s">
+      <c r="A8" s="143" t="s">
         <v>478</v>
       </c>
-      <c r="B8" s="140" t="s">
+      <c r="B8" s="145" t="s">
         <v>479</v>
       </c>
-      <c r="C8" s="139" t="s">
+      <c r="C8" s="144" t="s">
         <v>480</v>
       </c>
-      <c r="D8" s="142" t="s">
+      <c r="D8" s="147" t="s">
         <v>481</v>
       </c>
-      <c r="E8" s="139" t="s">
+      <c r="E8" s="144" t="s">
         <v>482</v>
       </c>
-      <c r="F8" s="140" t="s">
+      <c r="F8" s="145" t="s">
         <v>483</v>
       </c>
-      <c r="G8" s="141"/>
-      <c r="H8" s="141"/>
+      <c r="G8" s="146"/>
+      <c r="H8" s="146"/>
     </row>
     <row r="9" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="138" t="s">
+      <c r="A9" s="143" t="s">
         <v>484</v>
       </c>
-      <c r="B9" s="139" t="s">
+      <c r="B9" s="144" t="s">
         <v>485</v>
       </c>
-      <c r="C9" s="89" t="s">
+      <c r="C9" s="94" t="s">
         <v>486</v>
       </c>
-      <c r="D9" s="139" t="s">
+      <c r="D9" s="144" t="s">
         <v>487</v>
       </c>
-      <c r="E9" s="139" t="s">
+      <c r="E9" s="144" t="s">
         <v>488</v>
       </c>
-      <c r="F9" s="143" t="s">
+      <c r="F9" s="148" t="s">
         <v>489</v>
       </c>
-      <c r="G9" s="144"/>
-      <c r="H9" s="141"/>
+      <c r="G9" s="149"/>
+      <c r="H9" s="146"/>
     </row>
     <row r="10" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="138" t="s">
+      <c r="A10" s="143" t="s">
         <v>490</v>
       </c>
-      <c r="B10" s="139" t="s">
+      <c r="B10" s="144" t="s">
         <v>491</v>
       </c>
-      <c r="C10" s="139" t="s">
+      <c r="C10" s="144" t="s">
         <v>492</v>
       </c>
-      <c r="D10" s="139" t="s">
+      <c r="D10" s="144" t="s">
         <v>493</v>
       </c>
-      <c r="E10" s="145" t="s">
+      <c r="E10" s="150" t="s">
         <v>494</v>
       </c>
-      <c r="F10" s="140" t="s">
+      <c r="F10" s="145" t="s">
         <v>495</v>
       </c>
-      <c r="G10" s="141"/>
-      <c r="H10" s="141"/>
+      <c r="G10" s="146"/>
+      <c r="H10" s="146"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="39" t="s">
@@ -9863,11 +9435,11 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="151" t="s">
         <v>497</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="33" t="s">
@@ -9884,477 +9456,477 @@
       <c r="C4" s="42"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="147" t="s">
+      <c r="A6" s="152" t="s">
         <v>500</v>
       </c>
-      <c r="B6" s="147"/>
-      <c r="C6" s="147"/>
+      <c r="B6" s="152"/>
+      <c r="C6" s="152"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="148" t="s">
+      <c r="A7" s="153" t="s">
         <v>158</v>
       </c>
-      <c r="B7" s="149" t="s">
+      <c r="B7" s="154" t="s">
         <v>501</v>
       </c>
-      <c r="C7" s="149" t="s">
+      <c r="C7" s="154" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="150" t="s">
+      <c r="A8" s="155" t="s">
         <v>160</v>
       </c>
-      <c r="B8" s="151" t="s">
+      <c r="B8" s="156" t="s">
         <v>503</v>
       </c>
-      <c r="C8" s="152" t="s">
+      <c r="C8" s="157" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="153" t="s">
+      <c r="A9" s="158" t="s">
         <v>163</v>
       </c>
-      <c r="B9" s="154" t="s">
+      <c r="B9" s="159" t="s">
         <v>505</v>
       </c>
-      <c r="C9" s="155" t="s">
+      <c r="C9" s="160" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="153" t="s">
+      <c r="A10" s="158" t="s">
         <v>166</v>
       </c>
-      <c r="B10" s="154" t="s">
+      <c r="B10" s="159" t="s">
         <v>506</v>
       </c>
-      <c r="C10" s="155" t="s">
+      <c r="C10" s="160" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="153" t="s">
+      <c r="A11" s="158" t="s">
         <v>169</v>
       </c>
-      <c r="B11" s="154" t="s">
+      <c r="B11" s="159" t="s">
         <v>507</v>
       </c>
-      <c r="C11" s="155" t="s">
+      <c r="C11" s="160" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="153" t="s">
+      <c r="A12" s="158" t="s">
         <v>172</v>
       </c>
-      <c r="B12" s="154" t="s">
+      <c r="B12" s="159" t="s">
         <v>509</v>
       </c>
-      <c r="C12" s="155" t="s">
+      <c r="C12" s="160" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="153" t="s">
+      <c r="A13" s="158" t="s">
         <v>175</v>
       </c>
-      <c r="B13" s="154" t="s">
+      <c r="B13" s="159" t="s">
         <v>511</v>
       </c>
-      <c r="C13" s="155" t="s">
+      <c r="C13" s="160" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="156" t="s">
+      <c r="A14" s="161" t="s">
         <v>178</v>
       </c>
-      <c r="B14" s="157" t="s">
+      <c r="B14" s="162" t="s">
         <v>513</v>
       </c>
-      <c r="C14" s="158" t="s">
+      <c r="C14" s="163" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="156" t="s">
+      <c r="A15" s="161" t="s">
         <v>514</v>
       </c>
-      <c r="B15" s="157" t="s">
+      <c r="B15" s="162" t="s">
         <v>515</v>
       </c>
-      <c r="C15" s="158"/>
+      <c r="C15" s="163"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="156" t="s">
+      <c r="A16" s="161" t="s">
         <v>516</v>
       </c>
-      <c r="B16" s="159" t="s">
+      <c r="B16" s="164" t="s">
         <v>517</v>
       </c>
-      <c r="C16" s="158"/>
+      <c r="C16" s="163"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="156" t="s">
+      <c r="A17" s="161" t="s">
         <v>518</v>
       </c>
-      <c r="B17" s="159" t="s">
+      <c r="B17" s="164" t="s">
         <v>519</v>
       </c>
-      <c r="C17" s="158"/>
+      <c r="C17" s="163"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="156" t="s">
+      <c r="A18" s="161" t="s">
         <v>520</v>
       </c>
-      <c r="B18" s="89" t="s">
+      <c r="B18" s="94" t="s">
         <v>521</v>
       </c>
-      <c r="C18" s="158"/>
+      <c r="C18" s="163"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="160" t="s">
+      <c r="A19" s="165" t="s">
         <v>522</v>
       </c>
-      <c r="B19" s="160"/>
-      <c r="C19" s="160"/>
+      <c r="B19" s="165"/>
+      <c r="C19" s="165"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="161" t="s">
+      <c r="A20" s="166" t="s">
         <v>158</v>
       </c>
-      <c r="B20" s="149" t="s">
+      <c r="B20" s="154" t="s">
         <v>501</v>
       </c>
-      <c r="C20" s="149" t="s">
+      <c r="C20" s="154" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="33.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="162" t="s">
+      <c r="A21" s="167" t="s">
         <v>182</v>
       </c>
-      <c r="B21" s="163" t="s">
+      <c r="B21" s="168" t="s">
         <v>523</v>
       </c>
-      <c r="C21" s="152" t="s">
+      <c r="C21" s="157" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="164" t="s">
+      <c r="A22" s="169" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="165" t="s">
+      <c r="B22" s="170" t="s">
         <v>524</v>
       </c>
-      <c r="C22" s="155" t="s">
+      <c r="C22" s="160" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="164" t="s">
+      <c r="A23" s="169" t="s">
         <v>188</v>
       </c>
-      <c r="B23" s="154" t="s">
+      <c r="B23" s="159" t="s">
         <v>525</v>
       </c>
-      <c r="C23" s="155" t="s">
+      <c r="C23" s="160" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="164" t="s">
+      <c r="A24" s="169" t="s">
         <v>526</v>
       </c>
-      <c r="B24" s="166" t="s">
+      <c r="B24" s="171" t="s">
         <v>527</v>
       </c>
-      <c r="C24" s="155" t="s">
+      <c r="C24" s="160" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="164" t="s">
+      <c r="A25" s="169" t="s">
         <v>194</v>
       </c>
-      <c r="B25" s="154" t="s">
+      <c r="B25" s="159" t="s">
         <v>529</v>
       </c>
-      <c r="C25" s="155" t="s">
+      <c r="C25" s="160" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="49.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="167" t="s">
+      <c r="A26" s="172" t="s">
         <v>197</v>
       </c>
-      <c r="B26" s="168" t="s">
+      <c r="B26" s="173" t="s">
         <v>530</v>
       </c>
-      <c r="C26" s="158" t="s">
+      <c r="C26" s="163" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="169" t="s">
+      <c r="A27" s="174" t="s">
         <v>531</v>
       </c>
-      <c r="B27" s="159" t="s">
+      <c r="B27" s="164" t="s">
         <v>532</v>
       </c>
-      <c r="C27" s="158"/>
+      <c r="C27" s="163"/>
     </row>
     <row r="28" customFormat="false" ht="16.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="169" t="s">
+      <c r="A28" s="174" t="s">
         <v>533</v>
       </c>
-      <c r="B28" s="159" t="s">
+      <c r="B28" s="164" t="s">
         <v>534</v>
       </c>
-      <c r="C28" s="158"/>
+      <c r="C28" s="163"/>
     </row>
     <row r="29" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="170" t="s">
+      <c r="A29" s="175" t="s">
         <v>535</v>
       </c>
-      <c r="B29" s="171" t="s">
+      <c r="B29" s="176" t="s">
         <v>536</v>
       </c>
-      <c r="C29" s="158"/>
+      <c r="C29" s="163"/>
     </row>
     <row r="30" customFormat="false" ht="15.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="169" t="s">
+      <c r="A30" s="174" t="s">
         <v>537</v>
       </c>
-      <c r="B30" s="159" t="s">
+      <c r="B30" s="164" t="s">
         <v>538</v>
       </c>
-      <c r="C30" s="158"/>
+      <c r="C30" s="163"/>
     </row>
     <row r="31" customFormat="false" ht="16.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="169" t="s">
+      <c r="A31" s="174" t="s">
         <v>539</v>
       </c>
-      <c r="B31" s="159" t="s">
+      <c r="B31" s="164" t="s">
         <v>540</v>
       </c>
-      <c r="C31" s="158"/>
+      <c r="C31" s="163"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="172" t="s">
+      <c r="A32" s="177" t="s">
         <v>541</v>
       </c>
-      <c r="B32" s="172"/>
-      <c r="C32" s="172"/>
+      <c r="B32" s="177"/>
+      <c r="C32" s="177"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="173" t="s">
+      <c r="A33" s="178" t="s">
         <v>158</v>
       </c>
-      <c r="B33" s="149" t="s">
+      <c r="B33" s="154" t="s">
         <v>501</v>
       </c>
-      <c r="C33" s="149" t="s">
+      <c r="C33" s="154" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="36.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="174" t="s">
+      <c r="A34" s="179" t="s">
         <v>542</v>
       </c>
-      <c r="B34" s="163" t="s">
+      <c r="B34" s="168" t="s">
         <v>543</v>
       </c>
-      <c r="C34" s="152" t="s">
+      <c r="C34" s="157" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="38.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="175" t="s">
+      <c r="A35" s="180" t="s">
         <v>544</v>
       </c>
-      <c r="B35" s="176" t="s">
+      <c r="B35" s="181" t="s">
         <v>545</v>
       </c>
-      <c r="C35" s="155" t="s">
+      <c r="C35" s="160" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="175" t="s">
+      <c r="A36" s="180" t="s">
         <v>546</v>
       </c>
-      <c r="B36" s="154" t="s">
+      <c r="B36" s="159" t="s">
         <v>547</v>
       </c>
-      <c r="C36" s="155" t="s">
+      <c r="C36" s="160" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="177" t="s">
+      <c r="A37" s="182" t="s">
         <v>210</v>
       </c>
-      <c r="B37" s="168" t="s">
+      <c r="B37" s="173" t="s">
         <v>549</v>
       </c>
-      <c r="C37" s="158" t="s">
+      <c r="C37" s="163" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="178" t="s">
+      <c r="A38" s="183" t="s">
         <v>550</v>
       </c>
-      <c r="B38" s="178"/>
-      <c r="C38" s="178"/>
+      <c r="B38" s="183"/>
+      <c r="C38" s="183"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="179" t="s">
+      <c r="A39" s="184" t="s">
         <v>158</v>
       </c>
-      <c r="B39" s="149" t="s">
+      <c r="B39" s="154" t="s">
         <v>501</v>
       </c>
-      <c r="C39" s="149" t="s">
+      <c r="C39" s="154" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="180" t="s">
+      <c r="A40" s="185" t="s">
         <v>214</v>
       </c>
-      <c r="B40" s="181" t="s">
+      <c r="B40" s="186" t="s">
         <v>551</v>
       </c>
-      <c r="C40" s="152" t="s">
+      <c r="C40" s="157" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="182" t="s">
+      <c r="A41" s="187" t="s">
         <v>217</v>
       </c>
-      <c r="B41" s="166" t="s">
+      <c r="B41" s="171" t="s">
         <v>552</v>
       </c>
-      <c r="C41" s="155" t="s">
+      <c r="C41" s="160" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="182" t="s">
+      <c r="A42" s="187" t="s">
         <v>220</v>
       </c>
-      <c r="B42" s="166" t="s">
+      <c r="B42" s="171" t="s">
         <v>553</v>
       </c>
-      <c r="C42" s="155" t="s">
+      <c r="C42" s="160" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="182" t="s">
+      <c r="A43" s="187" t="s">
         <v>223</v>
       </c>
-      <c r="B43" s="154" t="s">
+      <c r="B43" s="159" t="s">
         <v>554</v>
       </c>
-      <c r="C43" s="155" t="s">
+      <c r="C43" s="160" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="183" t="s">
+      <c r="A44" s="188" t="s">
         <v>555</v>
       </c>
-      <c r="B44" s="159" t="s">
+      <c r="B44" s="164" t="s">
         <v>556</v>
       </c>
-      <c r="C44" s="158" t="s">
+      <c r="C44" s="163" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="184" t="s">
+      <c r="A45" s="189" t="s">
         <v>557</v>
       </c>
-      <c r="B45" s="159" t="s">
+      <c r="B45" s="164" t="s">
         <v>558</v>
       </c>
-      <c r="C45" s="158"/>
+      <c r="C45" s="163"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="41"/>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="185" t="s">
+      <c r="A47" s="190" t="s">
         <v>559</v>
       </c>
-      <c r="B47" s="185"/>
-      <c r="C47" s="185"/>
+      <c r="B47" s="190"/>
+      <c r="C47" s="190"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="186" t="s">
+      <c r="A48" s="191" t="s">
         <v>560</v>
       </c>
-      <c r="B48" s="186"/>
-      <c r="C48" s="186"/>
+      <c r="B48" s="191"/>
+      <c r="C48" s="191"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="187" t="s">
+      <c r="A49" s="192" t="s">
         <v>561</v>
       </c>
-      <c r="B49" s="188" t="s">
+      <c r="B49" s="193" t="s">
         <v>562</v>
       </c>
-      <c r="C49" s="188"/>
+      <c r="C49" s="193"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="189" t="s">
+      <c r="A50" s="194" t="s">
         <v>563</v>
       </c>
-      <c r="B50" s="190" t="s">
+      <c r="B50" s="195" t="s">
         <v>564</v>
       </c>
-      <c r="C50" s="190"/>
+      <c r="C50" s="195"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="189" t="s">
+      <c r="A51" s="194" t="s">
         <v>565</v>
       </c>
-      <c r="B51" s="191" t="s">
+      <c r="B51" s="196" t="s">
         <v>566</v>
       </c>
-      <c r="C51" s="191"/>
+      <c r="C51" s="196"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="189" t="s">
+      <c r="A52" s="194" t="s">
         <v>567</v>
       </c>
-      <c r="B52" s="191" t="s">
+      <c r="B52" s="196" t="s">
         <v>568</v>
       </c>
-      <c r="C52" s="191"/>
+      <c r="C52" s="196"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="192" t="s">
+      <c r="A53" s="197" t="s">
         <v>569</v>
       </c>
-      <c r="B53" s="193" t="s">
+      <c r="B53" s="198" t="s">
         <v>570</v>
       </c>
-      <c r="C53" s="193"/>
+      <c r="C53" s="198"/>
     </row>
     <row r="55" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="194" t="s">
+      <c r="A55" s="199" t="s">
         <v>571</v>
       </c>
-      <c r="B55" s="194"/>
-      <c r="C55" s="194"/>
+      <c r="B55" s="199"/>
+      <c r="C55" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -10402,26 +9974,26 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="195" t="s">
+      <c r="A1" s="200" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
+      <c r="B1" s="200"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="200"/>
+      <c r="G1" s="200"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="201" t="s">
         <v>572</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="196"/>
+      <c r="B2" s="201"/>
+      <c r="C2" s="201"/>
+      <c r="D2" s="201"/>
+      <c r="E2" s="201"/>
+      <c r="F2" s="201"/>
+      <c r="G2" s="201"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="42" t="s">
@@ -10435,176 +10007,176 @@
       <c r="G4" s="42"/>
     </row>
     <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="197" t="s">
+      <c r="A6" s="202" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="198" t="s">
+      <c r="B6" s="203" t="s">
         <v>574</v>
       </c>
-      <c r="C6" s="198" t="s">
+      <c r="C6" s="203" t="s">
         <v>575</v>
       </c>
-      <c r="D6" s="199" t="s">
+      <c r="D6" s="204" t="s">
         <v>576</v>
       </c>
-      <c r="E6" s="199" t="s">
+      <c r="E6" s="204" t="s">
         <v>577</v>
       </c>
-      <c r="F6" s="200" t="s">
+      <c r="F6" s="205" t="s">
         <v>578</v>
       </c>
-      <c r="G6" s="200" t="s">
+      <c r="G6" s="205" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="201" t="s">
+      <c r="A7" s="206" t="s">
         <v>580</v>
       </c>
-      <c r="B7" s="202" t="s">
+      <c r="B7" s="207" t="s">
         <v>581</v>
       </c>
-      <c r="C7" s="202" t="s">
+      <c r="C7" s="207" t="s">
         <v>582</v>
       </c>
-      <c r="D7" s="202" t="s">
+      <c r="D7" s="207" t="s">
         <v>583</v>
       </c>
-      <c r="E7" s="202" t="s">
+      <c r="E7" s="207" t="s">
         <v>584</v>
       </c>
-      <c r="F7" s="202" t="s">
+      <c r="F7" s="207" t="s">
         <v>585</v>
       </c>
-      <c r="G7" s="202" t="s">
+      <c r="G7" s="207" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="203" t="s">
+      <c r="A8" s="208" t="s">
         <v>587</v>
       </c>
-      <c r="B8" s="204" t="s">
+      <c r="B8" s="209" t="s">
         <v>588</v>
       </c>
-      <c r="C8" s="204" t="s">
+      <c r="C8" s="209" t="s">
         <v>589</v>
       </c>
-      <c r="D8" s="204" t="s">
+      <c r="D8" s="209" t="s">
         <v>590</v>
       </c>
-      <c r="E8" s="204" t="s">
+      <c r="E8" s="209" t="s">
         <v>591</v>
       </c>
-      <c r="F8" s="204" t="s">
+      <c r="F8" s="209" t="s">
         <v>592</v>
       </c>
-      <c r="G8" s="204" t="s">
+      <c r="G8" s="209" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="205" t="s">
+      <c r="A9" s="210" t="s">
         <v>594</v>
       </c>
-      <c r="B9" s="204" t="s">
+      <c r="B9" s="209" t="s">
         <v>595</v>
       </c>
-      <c r="C9" s="204" t="s">
+      <c r="C9" s="209" t="s">
         <v>596</v>
       </c>
-      <c r="D9" s="204" t="s">
+      <c r="D9" s="209" t="s">
         <v>597</v>
       </c>
-      <c r="E9" s="204" t="s">
+      <c r="E9" s="209" t="s">
         <v>598</v>
       </c>
-      <c r="F9" s="204" t="s">
+      <c r="F9" s="209" t="s">
         <v>599</v>
       </c>
-      <c r="G9" s="204" t="s">
+      <c r="G9" s="209" t="s">
         <v>600</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="205" t="s">
+      <c r="A10" s="210" t="s">
         <v>601</v>
       </c>
-      <c r="B10" s="204" t="s">
+      <c r="B10" s="209" t="s">
         <v>602</v>
       </c>
-      <c r="C10" s="204" t="s">
+      <c r="C10" s="209" t="s">
         <v>603</v>
       </c>
-      <c r="D10" s="204" t="s">
+      <c r="D10" s="209" t="s">
         <v>604</v>
       </c>
-      <c r="E10" s="204" t="s">
+      <c r="E10" s="209" t="s">
         <v>605</v>
       </c>
-      <c r="F10" s="204" t="s">
+      <c r="F10" s="209" t="s">
         <v>606</v>
       </c>
-      <c r="G10" s="204" t="s">
+      <c r="G10" s="209" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="205" t="s">
+      <c r="A11" s="210" t="s">
         <v>608</v>
       </c>
-      <c r="B11" s="204" t="s">
+      <c r="B11" s="209" t="s">
         <v>609</v>
       </c>
-      <c r="C11" s="204" t="s">
+      <c r="C11" s="209" t="s">
         <v>610</v>
       </c>
-      <c r="D11" s="204" t="s">
+      <c r="D11" s="209" t="s">
         <v>611</v>
       </c>
-      <c r="E11" s="204" t="s">
+      <c r="E11" s="209" t="s">
         <v>612</v>
       </c>
-      <c r="F11" s="204" t="s">
+      <c r="F11" s="209" t="s">
         <v>613</v>
       </c>
-      <c r="G11" s="204" t="s">
+      <c r="G11" s="209" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="206" t="s">
+      <c r="A12" s="211" t="s">
         <v>615</v>
       </c>
-      <c r="B12" s="207" t="s">
+      <c r="B12" s="212" t="s">
         <v>616</v>
       </c>
-      <c r="C12" s="207" t="s">
+      <c r="C12" s="212" t="s">
         <v>617</v>
       </c>
-      <c r="D12" s="207" t="s">
+      <c r="D12" s="212" t="s">
         <v>618</v>
       </c>
-      <c r="E12" s="207" t="s">
+      <c r="E12" s="212" t="s">
         <v>619</v>
       </c>
-      <c r="F12" s="207" t="s">
+      <c r="F12" s="212" t="s">
         <v>620</v>
       </c>
-      <c r="G12" s="207" t="s">
+      <c r="G12" s="212" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="208" t="s">
+      <c r="A14" s="213" t="s">
         <v>622</v>
       </c>
-      <c r="B14" s="208"/>
-      <c r="C14" s="208"/>
-      <c r="D14" s="208"/>
-      <c r="E14" s="208"/>
-      <c r="F14" s="208"/>
-      <c r="G14" s="208"/>
+      <c r="B14" s="213"/>
+      <c r="C14" s="213"/>
+      <c r="D14" s="213"/>
+      <c r="E14" s="213"/>
+      <c r="F14" s="213"/>
+      <c r="G14" s="213"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="39" t="s">
